--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3289</v>
+        <v>4393</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2516</v>
+        <v>3347</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1022</v>
+        <v>1518</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>437</v>
+        <v>629</v>
       </c>
       <c r="F11" s="12" t="n">
+        <v>607</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>409</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>307</v>
-      </c>
       <c r="H11" s="12" t="n">
-        <v>302</v>
+        <v>434</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>387</v>
+        <v>567</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>250</v>
+        <v>364</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>275</v>
+        <v>389</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>215</v>
+        <v>294</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,51 +925,51 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>200</v>
+        <v>289</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,51 +979,51 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>08078</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>CASORIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,39 +1087,39 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>5</v>
+        <v>372</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>136</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1141,28 +1141,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>192</v>
+        <v>257</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -1195,28 +1195,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>1</v>
@@ -1230,12 +1230,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08078</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CASORIA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1245,39 +1245,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>284</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>93</v>
-      </c>
       <c r="J19" s="12" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>176</v>
+        <v>253</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
@@ -1411,28 +1411,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>12</v>
@@ -1446,12 +1446,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1461,35 +1461,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>139</v>
+        <v>265</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1515,46 +1515,46 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1573,31 +1573,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>194</v>
+        <v>113</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1608,12 +1608,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1623,51 +1623,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1677,35 +1677,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>135</v>
+        <v>232</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="J27" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1716,12 +1716,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1731,35 +1731,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1770,12 +1770,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1785,35 +1785,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="I29" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K29" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J29" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="L29" s="12" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1824,12 +1824,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1839,51 +1839,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1893,51 +1893,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1947,51 +1947,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2001,51 +2001,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H33" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,51 +2055,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>08423</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VAIRANO PATENORA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2109,35 +2109,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2148,12 +2148,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>08423</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>VAIRANO PATENORA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2163,35 +2163,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2221,35 +2221,35 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2275,35 +2275,35 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>389</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1670951156812339</v>
+        <v>65</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>144</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.6597222222222222</v>
+        <v>95</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>147</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.01360544217687075</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>215</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.004651162790697674</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>144</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.7708333333333334</v>
+        <v>111</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>241</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.004149377593360996</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>134</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.007462686567164179</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>274</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.0072992700729927</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>233</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.02575107296137339</v>
+        <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>256</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.046875</v>
+        <v>12</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>265</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.007547169811320755</v>
+        <v>2</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>173</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.09826589595375723</v>
+        <v>17</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>113</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.1946902654867257</v>
+        <v>22</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>185</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.2216216216216216</v>
+        <v>41</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>113</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.01769911504424779</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>119</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.2689075630252101</v>
+        <v>32</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>93</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.6021505376344086</v>
+        <v>56</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>64</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.015625</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>95</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.2842105263157895</v>
+        <v>27</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>99</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.0101010101010101</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>107</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.02803738317757009</v>
+        <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4393</v>
+        <v>4670</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3347</v>
+        <v>3559</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1518</v>
+        <v>1660</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>629</v>
+        <v>663</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>08078</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CASORIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>44</v>
+        <v>288</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>45</v>
+        <v>398</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08078</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASORIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,39 +1087,39 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>234</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>372</v>
+        <v>46</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1141,28 +1141,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>6</v>
@@ -1207,16 +1207,16 @@
         <v>15</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>1</v>
@@ -1249,28 +1249,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>1</v>
@@ -1303,28 +1303,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>5</v>
@@ -1369,16 +1369,16 @@
         <v>3</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
@@ -1392,7 +1392,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1411,31 +1411,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1465,31 +1465,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="G23" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="I23" s="12" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1500,12 +1500,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1515,51 +1515,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1569,35 +1569,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1608,12 +1608,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1623,51 +1623,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1677,51 +1677,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1731,51 +1731,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="G28" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1785,51 +1785,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1839,39 +1839,39 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>197</v>
+        <v>117</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1897,47 +1897,47 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1947,51 +1947,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2001,51 +2001,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,39 +2055,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2113,19 +2113,19 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F35" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="G35" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>64</v>
-      </c>
       <c r="I35" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>14</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2167,28 +2167,28 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>3</v>
@@ -2242,14 +2242,14 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2296,14 +2296,14 @@
         <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -1134,7 +1134,11 @@
           <t>MERCOGLIANO</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>D'AMBROSIO RAFFAELLO</t>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4670</v>
+        <v>4925</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3559</v>
+        <v>3750</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1660</v>
+        <v>1778</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>663</v>
+        <v>699</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>599</v>
+        <v>632</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -875,47 +875,47 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>96</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,51 +925,51 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08078</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASORIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>288</v>
+        <v>56</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>398</v>
+        <v>47</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>08078</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CASORIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,39 +1087,39 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>50</v>
+        <v>308</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>46</v>
+        <v>420</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>1</v>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>MARIGLIANO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>149</v>
+        <v>285</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>142</v>
+        <v>310</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MARIGLIANO</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,39 +1303,39 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>273</v>
+        <v>154</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>296</v>
+        <v>150</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>5</v>
@@ -1373,16 +1373,16 @@
         <v>3</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>18</v>
@@ -1427,16 +1427,16 @@
         <v>23</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>2</v>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>12</v>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>2</v>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>17</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>154</v>
+        <v>256</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>120</v>
+        <v>199</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,39 +1735,39 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1850,32 +1850,32 @@
         <v>115</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>26</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>63</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>49</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>32</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1955,16 +1955,16 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>38</v>
@@ -1973,10 +1973,10 @@
         <v>12</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>1</v>
@@ -2066,7 +2066,7 @@
         <v>76</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>14</v>
@@ -2084,7 +2084,7 @@
         <v>18</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>30</v>
@@ -2117,28 +2117,28 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>43</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>13</v>
@@ -2183,16 +2183,16 @@
         <v>10</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>3</v>
@@ -2246,14 +2246,14 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2300,14 +2300,14 @@
         <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4925</v>
+        <v>5223</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3750</v>
+        <v>3976</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1778</v>
+        <v>1911</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>673</v>
+        <v>724</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>632</v>
+        <v>677</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>96</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>2</v>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MERCOGLIANO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>244</v>
+        <v>376</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>72</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MERCOGLIANO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,39 +1141,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>361</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>1</v>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>2</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F20" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>169</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L20" s="12" t="n">
         <v>154</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>161</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>150</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>5</v>
@@ -1373,16 +1373,16 @@
         <v>3</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>2</v>
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H26" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>149</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L26" s="12" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>41</v>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>2</v>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>32</v>
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>119</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L32" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>139</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>133</v>
-      </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>66</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>37</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>15</v>
@@ -2138,7 +2138,7 @@
         <v>36</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>13</v>
@@ -2183,7 +2183,7 @@
         <v>10</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>10</v>
@@ -2192,14 +2192,14 @@
         <v>30</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>8</v>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5223</v>
+        <v>5525</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3976</v>
+        <v>4209</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1911</v>
+        <v>2047</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>724</v>
+        <v>770</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>677</v>
+        <v>720</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>96</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>2</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>1</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>1</v>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>2</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>26</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>2</v>
@@ -1469,35 +1469,35 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>2</v>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>21</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>18</v>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>41</v>
@@ -1739,35 +1739,35 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>28</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,19 +1847,19 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>27</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>30</v>
@@ -1868,7 +1868,7 @@
         <v>50</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>32</v>
@@ -1904,13 +1904,13 @@
         <v>105</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>44</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>93</v>
@@ -1922,14 +1922,14 @@
         <v>10</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>1</v>
@@ -2009,35 +2009,35 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>30</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2063,28 +2063,28 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -2117,28 +2117,28 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
@@ -2171,28 +2171,28 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K36" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J36" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="L36" s="12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>3</v>
@@ -2225,28 +2225,28 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -2300,14 +2300,14 @@
         <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N38" headerRowCount="1">
-  <autoFilter ref="A10:N38"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O38" headerRowCount="1">
+  <autoFilter ref="A10:O38"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS 87 KM.25+340  VIALE DELLA LIBERTA, 4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>795</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>770</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>515</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>541</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>460</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S MARIA DEL POZZO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>330</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>196</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>305</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>355</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>301</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>377</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>305</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA N.SANTANGELO SNC</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>390</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>327</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA A.DIAZ</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>338</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>470</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>280</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>254</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA 11 SETTEMBRE</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>320</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>357</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>225</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>327</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>276</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>343</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>321</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA A FALCONE 224</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>171</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>233</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>LOCALITA' CAPODIMONTE SNC.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>112</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>47</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>47</v>
       </c>
       <c r="L26" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA GIANTURCO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>273</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA LEONARDO DA VINCI 14</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA NAZIONALE DELLE PUGLIE</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA FUORI PORTA ROMA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS 6 KM 172+300</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5525</v>
+        <v>5770</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4209</v>
+        <v>4382</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2047</v>
+        <v>2155</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>795</v>
+        <v>838</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>770</v>
+        <v>812</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>720</v>
+        <v>751</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>96</v>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>54</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>1</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>65</v>
@@ -1208,16 +1208,16 @@
         <v>48</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>1</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>92</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G20" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M20" s="12" t="n">
         <v>172</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>165</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>123</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
+          <t>LOCALITA' CAPODIMONTE SNC.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' CAPODIMONTE SNC.</t>
+          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>183</v>
+        <v>246</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>31</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>41</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>66</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>32</v>
@@ -2025,13 +2025,13 @@
         <v>105</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>44</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>93</v>
@@ -2050,24 +2050,24 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="H32" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M32" s="12" t="n">
+        <v>122</v>
+      </c>
+      <c r="N32" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="N32" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,39 +2136,39 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>6</v>
@@ -2211,16 +2211,16 @@
         <v>17</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>0</v>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>80</v>
-      </c>
       <c r="J35" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>20</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5770</v>
+        <v>6026</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4382</v>
+        <v>4553</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2155</v>
+        <v>2279</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>838</v>
+        <v>871</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>812</v>
+        <v>863</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>751</v>
+        <v>781</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>96</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>2</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>1</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>1</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>58</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>83</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1467,7 +1467,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MARIANO SEMMOLA 25</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1491,42 +1491,42 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>AGNANO ASTRONI</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>332</v>
+        <v>372</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' CAPODIMONTE SNC.</t>
+          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
+          <t>LOCALITA' CAPODIMONTE SNC.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>60</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>41</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>31</v>
@@ -1984,7 +1984,7 @@
         <v>54</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>32</v>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>66</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,35 +2081,35 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>30</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>1</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>6</v>
@@ -2211,16 +2211,16 @@
         <v>17</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>0</v>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>86</v>
-      </c>
       <c r="J35" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>1</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>20</v>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6026</v>
+        <v>6337</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4553</v>
+        <v>4770</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2279</v>
+        <v>2409</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>871</v>
+        <v>916</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>863</v>
+        <v>932</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>96</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>2</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>1</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>525</v>
+        <v>558</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>88</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>49</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>11</v>
@@ -1267,16 +1267,16 @@
         <v>21</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>1</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,52 +1373,52 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>189</v>
+        <v>378</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1432,42 +1432,42 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>360</v>
+        <v>202</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>299</v>
+        <v>191</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>AGNANO ASTRONI</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>MARIANO SEMMOLA 25</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H24" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="K24" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>86</v>
-      </c>
       <c r="L24" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>19</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="I27" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>92</v>
-      </c>
       <c r="J27" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>41</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>35</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>32</v>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>66</v>
+        <v>196</v>
       </c>
       <c r="H31" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>96</v>
-      </c>
       <c r="K31" s="12" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>82</v>
-      </c>
       <c r="K32" s="12" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J36" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="K36" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="M36" s="12" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2379,7 +2379,7 @@
         <v>50</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
         <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6337</v>
+        <v>6541</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4770</v>
+        <v>4921</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2409</v>
+        <v>2528</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>916</v>
+        <v>967</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>932</v>
+        <v>974</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>822</v>
+        <v>858</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>96</v>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>207</v>
+        <v>356</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>341</v>
+        <v>215</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I15" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>259</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>119</v>
+      </c>
+      <c r="L15" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J15" s="12" t="n">
-        <v>253</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>116</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="M15" s="12" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>304</v>
+        <v>365</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>172</v>
+        <v>262</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,52 +1373,52 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>378</v>
+        <v>205</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>315</v>
+        <v>204</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>202</v>
+        <v>394</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>36</v>
@@ -1562,19 +1562,19 @@
         <v>19</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>65</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>138</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>195</v>
-      </c>
       <c r="K24" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>65</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>44</v>
@@ -1689,7 +1689,7 @@
         <v>75</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>76</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>19</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>95</v>
@@ -1804,10 +1804,10 @@
         <v>54</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>41</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1966,13 +1966,13 @@
         <v>128</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>70</v>
@@ -1984,7 +1984,7 @@
         <v>54</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>32</v>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2081,35 +2081,35 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,35 +2140,35 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>30</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>1</v>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>22</v>
@@ -2279,7 +2279,7 @@
         <v>47</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>1</v>
@@ -2456,14 +2456,14 @@
         <v>13</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6541</v>
+        <v>6816</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4921</v>
+        <v>5137</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2528</v>
+        <v>2627</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>967</v>
+        <v>993</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>974</v>
+        <v>1008</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>858</v>
+        <v>884</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>103</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>113</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>231</v>
+        <v>284</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>356</v>
+        <v>221</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>215</v>
+        <v>376</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>347</v>
+        <v>385</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,52 +1373,52 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>204</v>
+        <v>358</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>394</v>
+        <v>216</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="K21" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="L21" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="L21" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="M21" s="12" t="n">
-        <v>337</v>
+        <v>216</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="H22" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="I22" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="J22" s="12" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>65</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>36</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>24</v>
@@ -1739,16 +1739,16 @@
         <v>76</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>19</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="I27" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="J27" s="12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>41</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>68</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>53</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>32</v>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="G32" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>70</v>
-      </c>
       <c r="H32" s="12" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,39 +2136,39 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G33" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>143</v>
-      </c>
       <c r="N33" s="12" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>31</v>
@@ -2220,7 +2220,7 @@
         <v>14</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>1</v>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2320,13 +2320,13 @@
         <v>82</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>43</v>
@@ -2338,7 +2338,7 @@
         <v>40</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0</v>
@@ -2447,16 +2447,16 @@
         <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6816</v>
+        <v>7116</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5137</v>
+        <v>5368</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2627</v>
+        <v>2784</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>993</v>
+        <v>1034</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1008</v>
+        <v>1032</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>659</v>
+        <v>690</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>884</v>
+        <v>918</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>634</v>
+        <v>667</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>221</v>
+        <v>402</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>376</v>
+        <v>231</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I15" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>286</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="L15" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="J15" s="12" t="n">
-        <v>268</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>93</v>
-      </c>
       <c r="M15" s="12" t="n">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>189</v>
+        <v>292</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>6</v>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>1</v>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>19</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>41</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>59</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>32</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>9</v>
@@ -2034,16 +2034,16 @@
         <v>18</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>172</v>
+        <v>72</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>24</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>13</v>
@@ -2338,7 +2338,7 @@
         <v>40</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2438,13 +2438,13 @@
         <v>35</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>15</v>
@@ -2456,14 +2456,14 @@
         <v>14</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7116</v>
+        <v>7422</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5368</v>
+        <v>5620</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2784</v>
+        <v>2934</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1034</v>
+        <v>1067</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1032</v>
+        <v>1072</v>
       </c>
       <c r="H11" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="I11" s="12" t="n">
         <v>690</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>665</v>
-      </c>
       <c r="J11" s="12" t="n">
-        <v>918</v>
+        <v>950</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>667</v>
+        <v>716</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>MERCOGLIANO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIA N.SANTANGELO SNC</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>402</v>
+        <v>444</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>3</v>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MERCOGLIANO</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA N.SANTANGELO SNC</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>27</v>
@@ -1208,19 +1208,19 @@
         <v>22</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>71</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>6</v>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,42 +1491,42 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>AGNANO ASTRONI</t>
+          <t>VIA A FALCONE 224</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,42 +1550,42 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>259</v>
+        <v>170</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>397</v>
+        <v>191</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA A FALCONE 224</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>178</v>
+        <v>408</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>19</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H27" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="I27" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>105</v>
-      </c>
       <c r="J27" s="12" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>41</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>46</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>70</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>58</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>32</v>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>68</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>1</v>
@@ -2140,35 +2140,35 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>31</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2202,13 +2202,13 @@
         <v>113</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>49</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>101</v>
@@ -2220,14 +2220,14 @@
         <v>10</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>68</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2261,13 +2261,13 @@
         <v>112</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>59</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>67</v>
@@ -2279,7 +2279,7 @@
         <v>50</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>6</v>
@@ -2447,13 +2447,13 @@
         <v>2</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>24</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">

--- a/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - COLASANTO GIOACCHINO.xlsx
@@ -684,13 +684,13 @@
         <v>28</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7422</v>
+        <v>7387</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5620</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2934</v>
+        <v>2870</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1072</v>
+        <v>1054</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>605</v>
@@ -863,14 +863,14 @@
         <v>111</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>237</v>
@@ -922,14 +922,14 @@
         <v>52</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>143</v>
@@ -981,31 +981,31 @@
         <v>103</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>242</v>
+        <v>403</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>417</v>
+        <v>240</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>111</v>
@@ -1158,14 +1158,14 @@
         <v>96</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>71</v>
@@ -1217,7 +1217,7 @@
         <v>152</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>2</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>54</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>130</v>
@@ -1276,7 +1276,7 @@
         <v>41</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>3</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>73</v>
@@ -1335,7 +1335,7 @@
         <v>103</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>14</v>
@@ -1385,7 +1385,7 @@
         <v>6</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>67</v>
@@ -1394,7 +1394,7 @@
         <v>51</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>6</v>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>243</v>
+        <v>462</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MARIANO SEMMOLA 25</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,39 +1487,39 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>PASTORE PIERLUIGI</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>468</v>
+        <v>235</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>86</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>113</v>
@@ -1571,10 +1571,10 @@
         <v>14</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>47</v>
@@ -1621,7 +1621,7 @@
         <v>25</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>69</v>
@@ -1630,7 +1630,7 @@
         <v>76</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>21</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>52</v>
@@ -1689,7 +1689,7 @@
         <v>90</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>80</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>57</v>
@@ -1748,10 +1748,10 @@
         <v>71</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>69</v>
@@ -1807,10 +1807,10 @@
         <v>36</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA LEONARDO DA VINCI 14</t>
+          <t>VIA NAZIONALE DELLE PUGLIE</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,32 +1841,32 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>LANZANTE DOMENICO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>46</v>
+        <v>235</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>198</v>
+        <v>307</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE DELLE PUGLIE</t>
+          <t>VIA LEONARDO DA VINCI 14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,32 +1900,32 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>195</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>369</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>238</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>313</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>39</v>
@@ -1984,10 +1984,10 @@
         <v>61</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2025,16 +2025,16 @@
         <v>129</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>19</v>
@@ -2043,7 +2043,7 @@
         <v>68</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>LANZANTE DOMENICO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,46 +2136,46 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,42 +2199,42 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIALE MADDALENA</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>13</v>
@@ -2338,7 +2338,7 @@
         <v>41</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>22</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>2</v>
@@ -2447,7 +2447,7 @@
         <v>2</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>1</v>
@@ -2456,7 +2456,7 @@
         <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
